--- a/social_media/questions/ravens_matrices/ravens_answer_key.xlsx
+++ b/social_media/questions/ravens_matrices/ravens_answer_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjagelka\Dartmouth College Dropbox\Tomas Jagelka\Social Media Project\intelligence test questions\ai_test_ravens_tasks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Evans\Documents\GitHub\social_media\social_media\questions\ravens_matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A331B9-469C-48B1-AFCA-642E9EBB3584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B4DE35-719C-4BFD-BFD1-75748CF41360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -375,13 +375,6 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF990000"/>
       </font>
@@ -443,6 +436,13 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -484,13 +484,13 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Claude time note"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Gemini answer"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Gemini result"/>
-    <tableColumn id="20" xr3:uid="{F9650507-AC8A-4716-AF0E-83EFBA3132D4}" name="Column3" dataDxfId="1">
+    <tableColumn id="20" xr3:uid="{F9650507-AC8A-4716-AF0E-83EFBA3132D4}" name="Column3" dataDxfId="7">
       <calculatedColumnFormula>IF(N2="","",IF(N2=$C2,1,0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Gemini time (sec)"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Gemini time note"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Notes"/>
-    <tableColumn id="17" xr3:uid="{6DA35B0B-1695-4639-AD9C-749FCACF9095}" name="Sum correct" dataDxfId="0">
+    <tableColumn id="17" xr3:uid="{6DA35B0B-1695-4639-AD9C-749FCACF9095}" name="Sum correct" dataDxfId="6">
       <calculatedColumnFormula>SUM(RavenResultsTable[[#This Row],[Column3]],RavenResultsTable[[#This Row],[Column2]],RavenResultsTable[[#This Row],[Column1]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -648,7 +648,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -726,18 +726,18 @@
         <v>17</v>
       </c>
       <c r="C2" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3">
         <v>5</v>
       </c>
       <c r="E2" s="3" t="str">
         <f t="shared" ref="E2:E37" si="0">IF(D2="","",IF(D2=$C2,"Correct","Incorrect"))</f>
-        <v>Incorrect</v>
+        <v>Correct</v>
       </c>
       <c r="F2" s="3">
         <f t="shared" ref="F2:F37" si="1">IF(D2="","",IF(D2=$C2,1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -778,7 +778,7 @@
       <c r="S2" s="3"/>
       <c r="T2">
         <f>SUM(RavenResultsTable[[#This Row],[Column3]],RavenResultsTable[[#This Row],[Column2]],RavenResultsTable[[#This Row],[Column1]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2993,26 +2993,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:F37">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$E2="Correct"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$E2="Incorrect"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K37">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$J2="Correct"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$J2="Incorrect"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:P37">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>$O2="Correct"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>$O2="Incorrect"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3031,12 +3031,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5">
+    <row r="1" spans="1:6" ht="15">
       <c r="A1" s="7" t="s">
         <v>56</v>
       </c>
@@ -3054,7 +3054,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="14.5">
+    <row r="3" spans="1:6">
       <c r="A3" s="9" t="s">
         <v>57</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" ht="14.5">
+    <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
         <v>58</v>
       </c>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B5" s="5">
         <f>IFERROR(COUNTIFS(Results!$A:$A,"C",Results!$E:$E,"Correct")/(COUNTIFS(Results!$A:$A,"C",Results!$E:$E,"Correct")+COUNTIFS(Results!$A:$A,"C",Results!$E:$E,"Incorrect")),"")</f>
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C5" s="5">
         <f>IFERROR(COUNTIFS(Results!$A:$A,"D",Results!$E:$E,"Correct")/(COUNTIFS(Results!$A:$A,"D",Results!$E:$E,"Correct")+COUNTIFS(Results!$A:$A,"D",Results!$E:$E,"Incorrect")),"")</f>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E5" s="5">
         <f>IFERROR(COUNTIFS(Results!$E:$E,"Correct")/(COUNTIFS(Results!$E:$E,"Correct")+COUNTIFS(Results!$E:$E,"Incorrect")),"")</f>
-        <v>0.55555555555555558</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F5" s="2">
         <f>(COUNTIFS(Results!$E:$E,"Correct")+COUNTIFS(Results!$E:$E,"Incorrect"))</f>
@@ -3167,7 +3167,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="14.5">
+    <row r="9" spans="1:6">
       <c r="A9" s="9" t="s">
         <v>67</v>
       </c>
@@ -3177,7 +3177,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" ht="14.5">
+    <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
         <v>58</v>
       </c>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B11" s="2" t="str">
         <f>COUNTIFS(Results!$A:$A,"C",Results!$E:$E,"Correct")&amp;"/"&amp;(COUNTIFS(Results!$A:$A,"C",Results!$E:$E,"Correct")+COUNTIFS(Results!$A:$A,"C",Results!$E:$E,"Incorrect"))</f>
-        <v>7/12</v>
+        <v>8/12</v>
       </c>
       <c r="C11" s="2" t="str">
         <f>COUNTIFS(Results!$A:$A,"D",Results!$E:$E,"Correct")&amp;"/"&amp;(COUNTIFS(Results!$A:$A,"D",Results!$E:$E,"Correct")+COUNTIFS(Results!$A:$A,"D",Results!$E:$E,"Incorrect"))</f>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="E11" s="2" t="str">
         <f>COUNTIFS(Results!$E:$E,"Correct")&amp;"/"&amp;(COUNTIFS(Results!$E:$E,"Correct")+COUNTIFS(Results!$E:$E,"Incorrect"))</f>
-        <v>20/36</v>
+        <v>21/36</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -3269,7 +3269,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6" ht="14.5">
+    <row r="15" spans="1:6">
       <c r="A15" s="9" t="s">
         <v>68</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" ht="14.5">
+    <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.5">
+    <row r="17" spans="1:6" ht="28">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -3375,7 +3375,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="14.5">
+    <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
         <v>71</v>
       </c>
@@ -3391,20 +3391,20 @@
       </c>
       <c r="B22" s="2" t="str">
         <f>IFERROR(INDEX(A5:A7,MATCH(MAX(E5:E7),E5:E7,0))&amp;" ("&amp;TEXT(MAX(E5:E7),"0.0%")&amp;")","")</f>
-        <v>ChatGPT (55.6%)</v>
+        <v>ChatGPT (58.3%)</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="57">
+    <row r="23" spans="1:6" ht="42">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B23" s="2" t="str">
         <f>IFERROR("ChatGPT (currently "&amp;TEXT(E5,"0.0%")&amp;" accuracy with immediate responses)","")</f>
-        <v>ChatGPT (currently 55.6% accuracy with immediate responses)</v>
+        <v>ChatGPT (currently 58.3% accuracy with immediate responses)</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
